--- a/data/trans_camb/IP19C06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Habitat-trans_camb.xlsx
@@ -682,42 +682,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,01</t>
+          <t>0,0; 5,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,0</t>
+          <t>-3,22; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,0</t>
+          <t>-3,23; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,0</t>
+          <t>-3,26; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,0</t>
+          <t>-1,68; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,99</t>
+          <t>-0,67; 2,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,74</t>
+          <t>-0,67; 1,6</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,16</t>
+          <t>0,34; 4,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 4,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,72</t>
+          <t>0,37; 3,02</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,96</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,71</t>
+          <t>0,28; 3,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,37 +1335,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,77</t>
+          <t>0,71; 6,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,01</t>
+          <t>-1,75; 3,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,0</t>
+          <t>-4,35; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,0</t>
+          <t>-4,38; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,11</t>
+          <t>-0,06; 3,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,0</t>
+          <t>-1,88; 0,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,86</t>
+          <t>-0,37; 2,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,0</t>
+          <t>0,32; 2,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,66</t>
+          <t>0,68; 2,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,35</t>
+          <t>-0,48; 1,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,38</t>
+          <t>-0,86; 0,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,17</t>
+          <t>-0,51; 1,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,21</t>
+          <t>0,1; 1,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,59</t>
+          <t>-0,21; 0,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,42</t>
+          <t>0,22; 1,5</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-61,01; —</t>
+          <t>-38,5; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,7; —</t>
+          <t>-13,05; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Habitat-trans_camb.xlsx
@@ -682,42 +682,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,44</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,0</t>
+          <t>-3,58; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,0</t>
+          <t>-3,25; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,0</t>
+          <t>-3,25; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,0</t>
+          <t>-1,37; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,12</t>
+          <t>-0,66; 2,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,6</t>
+          <t>-0,67; 1,86</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,25</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,02</t>
+          <t>0,37; 3,0</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,51</t>
+          <t>0,28; 3,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 5,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,27 +1335,27 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,56</t>
+          <t>0,79; 6,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,07</t>
+          <t>-1,57; 3,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 0,0</t>
+          <t>-3,87; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,0</t>
+          <t>-3,86; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,16</t>
+          <t>-0,37; 2,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,67</t>
+          <t>-0,35; 2,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,07</t>
+          <t>0,32; 2,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,68</t>
+          <t>0,71; 2,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,32</t>
+          <t>-0,46; 1,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,38</t>
+          <t>-0,87; 0,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,22</t>
+          <t>-0,53; 1,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,26</t>
+          <t>0,1; 1,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,55</t>
+          <t>-0,24; 0,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,5</t>
+          <t>0,2; 1,53</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-38,5; —</t>
+          <t>-57,42; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,05; —</t>
+          <t>-19,06; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,09</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,18</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,92; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>-3,81; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>-3,56; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,0</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,0</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,0</t>
+          <t>-1,81; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,09</t>
+          <t>-0,67; 1,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,86</t>
+          <t>-0,67; 1,91</t>
         </is>
       </c>
     </row>
@@ -730,39 +730,39 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>58,22%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,52</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,58</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,93</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,12</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,29; 3,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,0</t>
+          <t>0,23; 1,93</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,08</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,86</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,62</t>
         </is>
       </c>
     </row>
@@ -1109,37 +1109,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 4,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,33</t>
+          <t>0,0; 4,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,57</t>
+          <t>0,28; 3,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
     </row>
@@ -1167,22 +1167,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,77</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,77</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,63</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,83</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,92</t>
+          <t>-1,55; 3,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,87; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,96</t>
+          <t>-3,9; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,01</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,0</t>
+          <t>0,77; 6,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>-0,32; 3,11</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-1,89; 0,0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>-0,37; 2,92</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 0,0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-0,35; 2,79</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>83,74%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>308,09%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>308,09%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>260,15%</t>
+          <t>268,46%</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,91</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -1541,37 +1541,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,06</t>
+          <t>-0,44; 1,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>-0,82; 0,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,83</t>
+          <t>-0,58; 0,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,3</t>
+          <t>0,32; 2,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,38</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,19</t>
+          <t>0,7; 2,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,28</t>
+          <t>0,11; 1,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,53</t>
+          <t>0,17; 1,28</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>-43,6%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-43,6%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>442,67%</t>
+          <t>397,19%</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-57,42; —</t>
+          <t>-61,01; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,06; —</t>
+          <t>-18,61; —</t>
         </is>
       </c>
     </row>
